--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DDV_HRM-2031-0420/panel_11/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DDV_HRM-2031-0420/panel_11/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,12 +434,27 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Outer Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Inner Radius</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -451,23 +466,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.93775</v>
+        <v>16.81069</v>
       </c>
       <c r="D2" t="n">
-        <v>16.21251</v>
+        <v>16.51913</v>
       </c>
       <c r="E2" t="n">
-        <v>16.92741</v>
+        <v>16.76617</v>
       </c>
       <c r="F2" t="n">
-        <v>22.07821</v>
+        <v>55.70693</v>
       </c>
       <c r="G2" t="n">
-        <v>34.76286</v>
+        <v>43.96188</v>
+      </c>
+      <c r="H2" t="n">
+        <v>86.06225999999999</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.05115</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.83658</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +501,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.59581</v>
+        <v>16.90987</v>
       </c>
       <c r="D3" t="n">
-        <v>16.02534</v>
+        <v>16.68637</v>
       </c>
       <c r="E3" t="n">
-        <v>16.4656</v>
+        <v>16.87099</v>
       </c>
       <c r="F3" t="n">
-        <v>22.46745</v>
+        <v>55.44006</v>
       </c>
       <c r="G3" t="n">
-        <v>34.77425</v>
+        <v>42.95464</v>
+      </c>
+      <c r="H3" t="n">
+        <v>87.09618</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0509</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.83125</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +532,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.00547</v>
+        <v>16.79756</v>
       </c>
       <c r="D4" t="n">
-        <v>16.15085</v>
+        <v>16.67821</v>
       </c>
       <c r="E4" t="n">
-        <v>16.50596</v>
+        <v>16.74055</v>
       </c>
       <c r="F4" t="n">
-        <v>21.89068</v>
+        <v>55.85444</v>
       </c>
       <c r="G4" t="n">
-        <v>35.19551</v>
+        <v>43.5682</v>
+      </c>
+      <c r="H4" t="n">
+        <v>85.33028</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.05116</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.8394</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +563,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.83287</v>
+        <v>17.01558</v>
       </c>
       <c r="D5" t="n">
-        <v>16.07546</v>
+        <v>16.45345</v>
       </c>
       <c r="E5" t="n">
-        <v>16.9049</v>
+        <v>16.72654</v>
       </c>
       <c r="F5" t="n">
-        <v>22.05341</v>
+        <v>56.14189</v>
       </c>
       <c r="G5" t="n">
-        <v>35.19935</v>
+        <v>43.68159</v>
+      </c>
+      <c r="H5" t="n">
+        <v>86.98065</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.05201</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.85866</v>
       </c>
     </row>
     <row r="6">
@@ -543,19 +594,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.24873</v>
+        <v>17.18872</v>
       </c>
       <c r="D6" t="n">
-        <v>16.37178</v>
+        <v>16.63836</v>
       </c>
       <c r="E6" t="n">
-        <v>16.50702</v>
+        <v>17.05157</v>
       </c>
       <c r="F6" t="n">
-        <v>22.08273</v>
+        <v>56.75396</v>
       </c>
       <c r="G6" t="n">
-        <v>35.11923</v>
+        <v>43.01772</v>
+      </c>
+      <c r="H6" t="n">
+        <v>84.95616</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.05053</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.8615</v>
       </c>
     </row>
     <row r="7">
@@ -565,19 +625,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.81915</v>
+        <v>17.24397</v>
       </c>
       <c r="D7" t="n">
-        <v>16.71321</v>
+        <v>16.94573</v>
       </c>
       <c r="E7" t="n">
-        <v>16.73677</v>
+        <v>16.96644</v>
       </c>
       <c r="F7" t="n">
-        <v>22.34158</v>
+        <v>57.06491</v>
       </c>
       <c r="G7" t="n">
-        <v>34.53578</v>
+        <v>43.34078</v>
+      </c>
+      <c r="H7" t="n">
+        <v>85.38153</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.05131</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.84382</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +656,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.01217</v>
+        <v>17.02462</v>
       </c>
       <c r="D8" t="n">
-        <v>16.02994</v>
+        <v>16.61277</v>
       </c>
       <c r="E8" t="n">
-        <v>16.8279</v>
+        <v>16.88137</v>
       </c>
       <c r="F8" t="n">
-        <v>21.77793</v>
+        <v>56.78057</v>
       </c>
       <c r="G8" t="n">
-        <v>34.04131</v>
+        <v>42.85872</v>
+      </c>
+      <c r="H8" t="n">
+        <v>86.08974000000001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.05121</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.84725</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +687,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.97303</v>
+        <v>17.27166</v>
       </c>
       <c r="D9" t="n">
-        <v>15.44133</v>
+        <v>16.6108</v>
       </c>
       <c r="E9" t="n">
-        <v>16.90534</v>
+        <v>16.85768</v>
       </c>
       <c r="F9" t="n">
-        <v>21.79366</v>
+        <v>56.39399</v>
       </c>
       <c r="G9" t="n">
-        <v>34.50754</v>
+        <v>42.80912</v>
+      </c>
+      <c r="H9" t="n">
+        <v>86.51484000000001</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.05071</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.84405</v>
       </c>
     </row>
     <row r="10">
@@ -631,19 +718,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.87463</v>
+        <v>17.29292</v>
       </c>
       <c r="D10" t="n">
-        <v>16.02873</v>
+        <v>16.61148</v>
       </c>
       <c r="E10" t="n">
-        <v>16.81268</v>
+        <v>16.63038</v>
       </c>
       <c r="F10" t="n">
-        <v>22.08065</v>
+        <v>55.61649</v>
       </c>
       <c r="G10" t="n">
-        <v>34.60692</v>
+        <v>42.49437</v>
+      </c>
+      <c r="H10" t="n">
+        <v>85.51975</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.05108</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.84851</v>
       </c>
     </row>
     <row r="11">
@@ -664,15 +760,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Outer Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>Inner Radius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -686,26 +792,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.01221</v>
+        <v>16.95238</v>
       </c>
       <c r="D12" t="n">
-        <v>16.6543</v>
+        <v>16.92988</v>
       </c>
       <c r="E12" t="n">
-        <v>16.80712</v>
+        <v>16.93083</v>
       </c>
       <c r="F12" t="n">
-        <v>42.4591</v>
+        <v>56.06963</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05207</v>
+        <v>43.21934</v>
       </c>
       <c r="H12" t="n">
-        <v>1.85424</v>
+        <v>87.79226</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.05169</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.86282</v>
       </c>
     </row>
     <row r="13">
@@ -715,22 +827,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.17105</v>
+        <v>17.15378</v>
       </c>
       <c r="D13" t="n">
-        <v>17.01086</v>
+        <v>16.81403</v>
       </c>
       <c r="E13" t="n">
-        <v>16.96257</v>
+        <v>16.84343</v>
       </c>
       <c r="F13" t="n">
-        <v>42.57103</v>
+        <v>56.73196</v>
       </c>
       <c r="G13" t="n">
-        <v>0.04985</v>
+        <v>43.25965</v>
       </c>
       <c r="H13" t="n">
-        <v>1.87199</v>
+        <v>85.04268</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.05107</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.844</v>
       </c>
     </row>
     <row r="14">
@@ -740,22 +858,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.27019</v>
+        <v>16.93398</v>
       </c>
       <c r="D14" t="n">
-        <v>16.58602</v>
+        <v>16.58452</v>
       </c>
       <c r="E14" t="n">
-        <v>17.03198</v>
+        <v>16.71626</v>
       </c>
       <c r="F14" t="n">
-        <v>43.54902</v>
+        <v>57.17255</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05041</v>
+        <v>42.98057</v>
       </c>
       <c r="H14" t="n">
-        <v>1.85157</v>
+        <v>86.62164</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.04953</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.85538</v>
       </c>
     </row>
     <row r="15">
@@ -765,22 +889,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.14756</v>
+        <v>17.03065</v>
       </c>
       <c r="D15" t="n">
-        <v>16.61272</v>
+        <v>16.75128</v>
       </c>
       <c r="E15" t="n">
-        <v>16.69435</v>
+        <v>16.85488</v>
       </c>
       <c r="F15" t="n">
-        <v>42.67746</v>
+        <v>55.02361</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05121</v>
+        <v>43.35942</v>
       </c>
       <c r="H15" t="n">
-        <v>1.82665</v>
+        <v>85.94171</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.05138</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.86018</v>
       </c>
     </row>
     <row r="16">
@@ -790,22 +920,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.11041</v>
+        <v>16.94111</v>
       </c>
       <c r="D16" t="n">
-        <v>16.71139</v>
+        <v>16.52989</v>
       </c>
       <c r="E16" t="n">
-        <v>17.27345</v>
+        <v>16.80326</v>
       </c>
       <c r="F16" t="n">
-        <v>42.7474</v>
+        <v>56.41406</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05197</v>
+        <v>42.99724</v>
       </c>
       <c r="H16" t="n">
-        <v>1.84893</v>
+        <v>87.85083</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.05199</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.8474</v>
       </c>
     </row>
     <row r="17">
@@ -815,22 +951,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.20698</v>
+        <v>16.93987</v>
       </c>
       <c r="D17" t="n">
-        <v>16.63589</v>
+        <v>16.91498</v>
       </c>
       <c r="E17" t="n">
-        <v>17.20236</v>
+        <v>16.93108</v>
       </c>
       <c r="F17" t="n">
-        <v>43.07356</v>
+        <v>56.87714</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05193</v>
+        <v>42.59794</v>
       </c>
       <c r="H17" t="n">
-        <v>1.86038</v>
+        <v>86.30992000000001</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.05224</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.86587</v>
       </c>
     </row>
     <row r="18">
@@ -840,22 +982,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.84814</v>
+        <v>17.16593</v>
       </c>
       <c r="D18" t="n">
-        <v>16.77336</v>
+        <v>16.7801</v>
       </c>
       <c r="E18" t="n">
-        <v>16.92602</v>
+        <v>16.86595</v>
       </c>
       <c r="F18" t="n">
-        <v>43.45108</v>
+        <v>55.7545</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05112</v>
+        <v>42.53696</v>
       </c>
       <c r="H18" t="n">
-        <v>1.85048</v>
+        <v>85.94692000000001</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.05177</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.84466</v>
       </c>
     </row>
     <row r="19">
@@ -865,22 +1013,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.24412</v>
+        <v>16.81442</v>
       </c>
       <c r="D19" t="n">
-        <v>16.7534</v>
+        <v>16.78672</v>
       </c>
       <c r="E19" t="n">
-        <v>17.02008</v>
+        <v>16.78952</v>
       </c>
       <c r="F19" t="n">
-        <v>42.89872</v>
+        <v>56.38032</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05012</v>
+        <v>43.02079</v>
       </c>
       <c r="H19" t="n">
-        <v>1.82526</v>
+        <v>85.43387</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.80836</v>
       </c>
     </row>
     <row r="20">
@@ -890,63 +1044,54 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.82815</v>
+        <v>17.06298</v>
       </c>
       <c r="D20" t="n">
-        <v>16.68566</v>
+        <v>16.49305</v>
       </c>
       <c r="E20" t="n">
-        <v>16.88954</v>
+        <v>17.0431</v>
       </c>
       <c r="F20" t="n">
-        <v>42.57215</v>
+        <v>57.30855</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05178</v>
+        <v>43.58211</v>
       </c>
       <c r="H20" t="n">
-        <v>1.83608</v>
+        <v>85.76291000000001</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.05085</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.84932</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rz mean</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rz min</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -958,32 +1103,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.76083</v>
+        <v>16.85132</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08202</v>
+        <v>16.38307</v>
       </c>
       <c r="E22" t="n">
-        <v>0.62421</v>
+        <v>16.65</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9854000000000001</v>
+        <v>22.12937</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1128</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.00767</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.0936</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.12697</v>
+        <v>35.3505</v>
       </c>
     </row>
     <row r="23">
@@ -993,28 +1129,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.76098</v>
+        <v>16.73783</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0809</v>
+        <v>16.09012</v>
       </c>
       <c r="E23" t="n">
-        <v>0.61585</v>
+        <v>16.45534</v>
       </c>
       <c r="F23" t="n">
-        <v>0.96165</v>
+        <v>22.37799</v>
       </c>
       <c r="G23" t="n">
-        <v>0.11078</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.00768</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.09388000000000001</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.12758</v>
+        <v>34.74405</v>
       </c>
     </row>
     <row r="24">
@@ -1024,28 +1151,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.73813</v>
+        <v>16.91238</v>
       </c>
       <c r="D24" t="n">
-        <v>0.083</v>
+        <v>16.32738</v>
       </c>
       <c r="E24" t="n">
-        <v>0.61306</v>
+        <v>16.76701</v>
       </c>
       <c r="F24" t="n">
-        <v>0.97098</v>
+        <v>21.88827</v>
       </c>
       <c r="G24" t="n">
-        <v>0.11042</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.00755</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09521</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.12762</v>
+        <v>35.24067</v>
       </c>
     </row>
     <row r="25">
@@ -1055,28 +1173,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.76416</v>
+        <v>16.67452</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08230999999999999</v>
+        <v>16.35541</v>
       </c>
       <c r="E25" t="n">
-        <v>0.61093</v>
+        <v>16.67113</v>
       </c>
       <c r="F25" t="n">
-        <v>0.96792</v>
+        <v>22.20666</v>
       </c>
       <c r="G25" t="n">
-        <v>0.11021</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.00765</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.09495000000000001</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.12899</v>
+        <v>35.34378</v>
       </c>
     </row>
     <row r="26">
@@ -1086,28 +1195,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.76745</v>
+        <v>17.09513</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08169</v>
+        <v>16.51475</v>
       </c>
       <c r="E26" t="n">
-        <v>0.62221</v>
+        <v>16.57253</v>
       </c>
       <c r="F26" t="n">
-        <v>0.97963</v>
+        <v>21.79816</v>
       </c>
       <c r="G26" t="n">
-        <v>0.11095</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.00772</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09283</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.12746</v>
+        <v>34.27055</v>
       </c>
     </row>
     <row r="27">
@@ -1117,28 +1217,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.7584</v>
+        <v>17.0272</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08085000000000001</v>
+        <v>15.99132</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6104000000000001</v>
+        <v>16.80027</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9704700000000001</v>
+        <v>22.15331</v>
       </c>
       <c r="G27" t="n">
-        <v>0.11091</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.00767</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09526</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.12927</v>
+        <v>34.47198</v>
       </c>
     </row>
     <row r="28">
@@ -1148,28 +1239,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.76872</v>
+        <v>16.92222</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0827</v>
+        <v>16.24636</v>
       </c>
       <c r="E28" t="n">
-        <v>0.61734</v>
+        <v>16.39128</v>
       </c>
       <c r="F28" t="n">
-        <v>0.95639</v>
+        <v>22.00612</v>
       </c>
       <c r="G28" t="n">
-        <v>0.10886</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.0076</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09619999999999999</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.13109</v>
+        <v>34.51145</v>
       </c>
     </row>
     <row r="29">
@@ -1179,28 +1261,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.77084</v>
+        <v>17.04951</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08269</v>
+        <v>16.42284</v>
       </c>
       <c r="E29" t="n">
-        <v>0.62157</v>
+        <v>16.77</v>
       </c>
       <c r="F29" t="n">
-        <v>0.96491</v>
+        <v>21.81493</v>
       </c>
       <c r="G29" t="n">
-        <v>0.11133</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.00775</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09390999999999999</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.12728</v>
+        <v>34.33811</v>
       </c>
     </row>
     <row r="30">
@@ -1210,28 +1283,345 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.74703</v>
+        <v>16.95979</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08055</v>
+        <v>16.24037</v>
       </c>
       <c r="E30" t="n">
-        <v>0.62553</v>
+        <v>16.53404</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9658</v>
+        <v>21.63023</v>
       </c>
       <c r="G30" t="n">
-        <v>0.11064</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.00775</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.0958</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.12782</v>
+        <v>34.32982</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.76034</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.08262</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.61542</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.96432</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.11012</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.00781</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09551</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.12811</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.75204</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.08207</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6257200000000001</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.97617</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.1086</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.00751</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09319</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.12581</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.74952</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.08212999999999999</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.61813</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.96968</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.11157</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.00769</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09427000000000001</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.13161</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7537199999999999</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.08260000000000001</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.61025</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.97397</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.10984</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.09302000000000001</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.12894</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.77882</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.08051</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.62478</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.99056</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.10858</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.09381</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.12814</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.74395</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.08105999999999999</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.59946</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.98031</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.11175</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09592000000000001</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.12471</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.76827</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.08046</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.62443</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.96231</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.11195</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.00755</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.12867</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7637699999999999</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.08182</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.61116</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.97428</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.11132</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.09456000000000001</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.12851</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7426199999999999</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.08369</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6362</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.00003</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.11112</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.09243999999999999</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.12808</v>
       </c>
     </row>
   </sheetData>
